--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487600_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487600_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6545</v>
+        <v>9.1557</v>
       </c>
       <c r="E2" t="n">
-        <v>10.4236</v>
+        <v>8.8431</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2309</v>
+        <v>0.3126</v>
       </c>
       <c r="G2" t="n">
         <v>3.5686</v>
@@ -610,13 +610,13 @@
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6561</v>
+        <v>0.1573</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9374</v>
+        <v>1.3568</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2813</v>
+        <v>-1.1995</v>
       </c>
       <c r="V2" t="n">
         <v>4.8477</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6017</v>
+        <v>2.8019</v>
       </c>
       <c r="E3" t="n">
-        <v>1.862</v>
+        <v>2.0622</v>
       </c>
       <c r="F3" t="n">
         <v>0.7398</v>
@@ -688,10 +688,10 @@
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2494</v>
+        <v>-1.0492</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4229</v>
+        <v>-0.2227</v>
       </c>
       <c r="U3" t="n">
         <v>-0.8266</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0633</v>
+        <v>2.3151</v>
       </c>
       <c r="E4" t="n">
-        <v>2.01</v>
+        <v>2.3709</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0533</v>
+        <v>-0.0557</v>
       </c>
       <c r="G4" t="n">
         <v>1.2264</v>
@@ -766,13 +766,13 @@
         <v>2.3284</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3109</v>
+        <v>-1.059</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0258</v>
+        <v>0.3866</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.3366</v>
+        <v>-1.4457</v>
       </c>
       <c r="V4" t="n">
         <v>2.7298</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4069</v>
+        <v>0.8133</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1695</v>
+        <v>0.6304</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2374</v>
+        <v>0.1829</v>
       </c>
       <c r="G5" t="n">
         <v>-1.8601</v>
@@ -844,13 +844,13 @@
         <v>2.1344</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0435</v>
+        <v>-0.637</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2771</v>
+        <v>0.1839</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7664</v>
+        <v>-0.8209</v>
       </c>
       <c r="V5" t="n">
         <v>1.1761</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2918</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4453</v>
+        <v>-0.0844</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7371</v>
+        <v>0.7916</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7776</v>
@@ -922,13 +922,13 @@
         <v>2.5224</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8127</v>
+        <v>-0.3973</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1559</v>
+        <v>0.2049</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6022</v>
       </c>
       <c r="V6" t="n">
         <v>0.3299</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8155</v>
+        <v>-0.3545</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5809</v>
+        <v>-0.12</v>
       </c>
       <c r="F7" t="n">
         <v>-0.2345</v>
@@ -1000,10 +1000,10 @@
         <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.504</v>
+        <v>-1.0431</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6057</v>
+        <v>-0.1447</v>
       </c>
       <c r="U7" t="n">
         <v>-0.8984</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0081</v>
+        <v>-0.5382</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3422</v>
+        <v>0.0187</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6659</v>
+        <v>-0.5569</v>
       </c>
       <c r="G8" t="n">
         <v>0.1866</v>
@@ -1078,13 +1078,13 @@
         <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0186</v>
+        <v>-0.5487</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.424</v>
+        <v>-0.0631</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5946</v>
+        <v>-0.4856</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5642</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9122</v>
+        <v>-2.7614</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.5036</v>
+        <v>-5.2438</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5914</v>
+        <v>2.4824</v>
       </c>
       <c r="G9" t="n">
         <v>-3.3369</v>
@@ -1156,13 +1156,13 @@
         <v>2.3284</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1038</v>
+        <v>0.2546</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9724</v>
+        <v>0.2321</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1315</v>
+        <v>0.0225</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0373</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5616</v>
+        <v>-2.9982</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9373</v>
+        <v>-4.2376</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3756</v>
+        <v>1.2393</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8663999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>1.9403</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.443</v>
+        <v>-0.8796</v>
       </c>
       <c r="T10" t="n">
-        <v>0.305</v>
+        <v>0.0047</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.748</v>
+        <v>-0.8843</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2821</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.065200000000001</v>
+        <v>-6.8796</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.8235</v>
+        <v>-5.8015</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2417</v>
+        <v>-1.0782</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3531</v>
@@ -1312,13 +1312,13 @@
         <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.6568</v>
+        <v>-1.4712</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7627</v>
+        <v>0.2593</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.8941</v>
+        <v>-1.7305</v>
       </c>
       <c r="V11" t="n">
         <v>2.2134</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.655599999999998</v>
+        <v>2.261299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.167700000000001</v>
+        <v>-1.561999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.823399999999999</v>
+        <v>3.823300000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8086000000000007</v>
@@ -1390,13 +1390,13 @@
         <v>17.4631</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.279</v>
+        <v>-6.6732</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5923</v>
+        <v>2.1978</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.8713</v>
+        <v>-8.871199999999998</v>
       </c>
       <c r="V12" t="n">
         <v>9.743200000000002</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.0678</v>
+        <v>2.5822</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1061</v>
+        <v>0.4522</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1738</v>
+        <v>2.13</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4915</v>
+        <v>1.5105</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3569</v>
+        <v>2.3752</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8484</v>
+        <v>-0.8647</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5097</v>
+        <v>1.2191</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7538</v>
+        <v>3.8022</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2635</v>
+        <v>-2.5831</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9818</v>
+        <v>0.2914</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6031</v>
+        <v>-1.427</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5849</v>
+        <v>1.7183</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1344</v>
+        <v>-2.3284</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7164</v>
+        <v>3.1045</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5583</v>
+        <v>0.9553</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5186</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9603</v>
+        <v>0.2401</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5642</v>
+        <v>-0.6597</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.8462</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5642</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. KHIVRENKO</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0119</v>
+        <v>2.4437</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0408</v>
+        <v>-0.1061</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.029</v>
+        <v>2.5498</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0406</v>
+        <v>1.4915</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9244</v>
+        <v>-1.3569</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1162</v>
+        <v>2.8484</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4812</v>
+        <v>0.5097</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3594</v>
+        <v>-0.7538</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1218</v>
+        <v>1.2635</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4406</v>
+        <v>0.9818</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.435</v>
+        <v>-0.6031</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0056</v>
+        <v>1.5849</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9702</v>
+        <v>-2.1344</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7761</v>
+        <v>2.7164</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7772</v>
+        <v>0.9343</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5298</v>
+        <v>1.5186</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2474</v>
+        <v>-0.5843</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6119</v>
+        <v>-0.5642</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6119</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9033</v>
+        <v>1.8573</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2785</v>
+        <v>-0.6788</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1818</v>
+        <v>2.5361</v>
       </c>
       <c r="G15" t="n">
         <v>1.6879</v>
@@ -1624,13 +1624,13 @@
         <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0915</v>
+        <v>0.0454</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4867</v>
+        <v>0.0863</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3952</v>
+        <v>-0.0409</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8462</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>M. KHIVRENKO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4322</v>
+        <v>1.1204</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6489</v>
+        <v>1.3401</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0811</v>
+        <v>-0.2197</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5105</v>
+        <v>1.0406</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3752</v>
+        <v>0.9244</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8647</v>
+        <v>0.1162</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2191</v>
+        <v>1.4812</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8022</v>
+        <v>1.3594</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.5831</v>
+        <v>0.1218</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2914</v>
+        <v>-0.4406</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.427</v>
+        <v>-0.435</v>
       </c>
       <c r="O16" t="n">
-        <v>1.7183</v>
+        <v>-0.0056</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.7761</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-2.3284</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.1045</v>
-      </c>
       <c r="S16" t="n">
-        <v>-0.1947</v>
+        <v>0.8858</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3859</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1912</v>
+        <v>0.0567</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6597</v>
+        <v>-0.6119</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8462</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.506</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1339</v>
+        <v>0.9606</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4258</v>
+        <v>0.9263</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5598</v>
+        <v>0.0342</v>
       </c>
       <c r="G17" t="n">
         <v>0.7114</v>
@@ -1780,13 +1780,13 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5334</v>
+        <v>0.5611</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2927</v>
+        <v>0.7932</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.2321</v>
       </c>
       <c r="V17" t="n">
         <v>-0.894</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>L. GIFREU LLARCH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5955</v>
+        <v>-0.0401</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.205</v>
+        <v>-1.417</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3905</v>
+        <v>1.3769</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0282</v>
+        <v>-1.1643</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2589</v>
+        <v>-3.8153</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2306</v>
+        <v>2.651</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0406</v>
+        <v>-0.7995</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-2.1214</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0406</v>
+        <v>1.3219</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0688</v>
+        <v>-0.3648</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2589</v>
+        <v>-1.6939</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1901</v>
+        <v>1.3291</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3582</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2985</v>
+        <v>-2.9105</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9403</v>
+        <v>2.3284</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2386</v>
+        <v>1.0944</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4887</v>
+        <v>0.787</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7499</v>
+        <v>0.3073</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4477</v>
+        <v>0.6119</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5642</v>
+        <v>1.506</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.0119</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. GIFREU LLARCH</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6262</v>
+        <v>-1.4997</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1177</v>
+        <v>-1.3043</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4915</v>
+        <v>-0.1954</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1643</v>
+        <v>-2.3403</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.8153</v>
+        <v>-2.7641</v>
       </c>
       <c r="I19" t="n">
-        <v>2.651</v>
+        <v>0.4237</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7995</v>
+        <v>-1.4153</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1214</v>
+        <v>-1.5777</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3219</v>
+        <v>0.1624</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3648</v>
+        <v>-0.925</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6939</v>
+        <v>-1.1864</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3291</v>
+        <v>0.2614</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9105</v>
+        <v>-1.3582</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3284</v>
+        <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5083</v>
+        <v>1.5107</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0863</v>
+        <v>1.4692</v>
       </c>
       <c r="U19" t="n">
-        <v>0.422</v>
+        <v>0.0415</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6119</v>
+        <v>-0.2821</v>
       </c>
       <c r="W19" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0448</v>
+        <v>-2.3907</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9039</v>
+        <v>-1.8066</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1409</v>
+        <v>-0.5841</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3403</v>
+        <v>-0.0282</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.7641</v>
+        <v>-1.2589</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4237</v>
+        <v>1.2306</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4153</v>
+        <v>0.0406</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.5777</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1624</v>
+        <v>0.0406</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.925</v>
+        <v>-0.0688</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1864</v>
+        <v>-1.2589</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2614</v>
+        <v>1.1901</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3881</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3582</v>
+        <v>-3.2985</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9656</v>
+        <v>1.4435</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8696</v>
+        <v>0.8871</v>
       </c>
       <c r="U20" t="n">
-        <v>0.096</v>
+        <v>0.5563</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2821</v>
+        <v>-2.4477</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2821</v>
+        <v>-3.0119</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9756</v>
+        <v>-2.5663</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2189</v>
+        <v>-2.9186</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2432</v>
+        <v>0.3523</v>
       </c>
       <c r="G21" t="n">
         <v>-0.851</v>
@@ -2092,13 +2092,13 @@
         <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2425</v>
+        <v>0.1668</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0852</v>
+        <v>0.3855</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3277</v>
+        <v>-0.2187</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3299</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6948</v>
+        <v>-2.7882</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9069</v>
+        <v>1.4074</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.6016</v>
+        <v>-4.1956</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2495</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1099</v>
+        <v>1.0164</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8995</v>
+        <v>1.4</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7896</v>
+        <v>-0.3835</v>
       </c>
       <c r="V22" t="n">
         <v>-3.7194</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.655600000000001</v>
+        <v>-0.3207999999999984</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1055</v>
+        <v>-4.1054</v>
       </c>
       <c r="F23" t="n">
-        <v>2.449599999999999</v>
+        <v>3.7845</v>
       </c>
       <c r="G23" t="n">
         <v>0.8085999999999995</v>
@@ -2218,28 +2218,28 @@
         <v>-7.2829</v>
       </c>
       <c r="I23" t="n">
-        <v>8.0914</v>
+        <v>8.091399999999998</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1705</v>
+        <v>-0.1705000000000002</v>
       </c>
       <c r="K23" t="n">
-        <v>1.664399999999999</v>
+        <v>1.6644</v>
       </c>
       <c r="L23" t="n">
         <v>-1.8349</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9790999999999999</v>
+        <v>0.9791000000000003</v>
       </c>
       <c r="N23" t="n">
         <v>-8.9474</v>
       </c>
       <c r="O23" t="n">
-        <v>9.926400000000001</v>
+        <v>9.926399999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-17.4629</v>
@@ -2248,13 +2248,13 @@
         <v>17.4629</v>
       </c>
       <c r="S23" t="n">
-        <v>7.278799999999999</v>
+        <v>8.613700000000001</v>
       </c>
       <c r="T23" t="n">
         <v>8.8712</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.5924</v>
+        <v>-0.2576000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-9.7432</v>
